--- a/static/templates/delivery_template.xlsx
+++ b/static/templates/delivery_template.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="419">
   <si>
     <t xml:space="preserve">기준정보 입력</t>
   </si>
@@ -722,6 +722,21 @@
   </si>
   <si>
     <t>MTPF-201-5-2</t>
+  </si>
+  <si>
+    <t>MT-RS138-SW</t>
+  </si>
+  <si>
+    <t>46161585</t>
+  </si>
+  <si>
+    <t>도로표지병</t>
+  </si>
+  <si>
+    <t>Φ138×47mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">백색, 태양광/LED,점등형</t>
   </si>
   <si>
     <t>END</t>
@@ -10664,7 +10679,7 @@
         <v>218</v>
       </c>
       <c r="B136" s="12" t="str">
-        <f t="shared" ref="B136" si="2">IF($G136="","-",CONCATENATE(F136," ",G136," ",H136," ",I136," ",K136," ",L136))</f>
+        <f t="shared" ref="B136:B199" si="2">IF($G136="","-",CONCATENATE(F136," ",G136," ",H136," ",I136," ",K136," ",L136))</f>
         <v xml:space="preserve"> 철제가로등주 MTPF-201-5 5m 1등용 </v>
       </c>
       <c r="C136" s="13">
@@ -10699,7 +10714,7 @@
         <v>220</v>
       </c>
       <c r="B137" s="12" t="str">
-        <f t="shared" ref="B137:B200" si="3">IF($G137="","-",CONCATENATE(F137," ",G137," ",H137," ",I137," ",K137," ",L137))</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> 철제가로등주 MTPF-201-5-2 5m 2등용 </v>
       </c>
       <c r="C137" s="13">
@@ -10730,26 +10745,44 @@
       <c r="L137" s="11"/>
     </row>
     <row r="138">
-      <c r="A138" s="11"/>
+      <c r="A138" s="11" t="s">
+        <v>221</v>
+      </c>
       <c r="B138" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
-      </c>
-      <c r="C138" s="13"/>
-      <c r="D138" s="14"/>
-      <c r="E138" s="11"/>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> 도로표지병 MT-RS138-SW Φ138×47mm 백색, 태양광/LED,점등형 </v>
+      </c>
+      <c r="C138" s="13">
+        <v>88000</v>
+      </c>
+      <c r="D138" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="E138" s="11" t="s">
+        <v>223</v>
+      </c>
       <c r="F138" s="11"/>
-      <c r="G138" s="11"/>
-      <c r="H138" s="11"/>
-      <c r="I138" s="11"/>
-      <c r="J138" s="11"/>
-      <c r="K138" s="11"/>
+      <c r="G138" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H138" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="I138" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="J138" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138" s="11" t="s">
+        <v>225</v>
+      </c>
       <c r="L138" s="11"/>
     </row>
     <row r="139">
       <c r="A139" s="11"/>
       <c r="B139" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C139" s="13"/>
@@ -10766,7 +10799,7 @@
     <row r="140">
       <c r="A140" s="11"/>
       <c r="B140" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C140" s="13"/>
@@ -10783,7 +10816,7 @@
     <row r="141">
       <c r="A141" s="11"/>
       <c r="B141" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C141" s="13"/>
@@ -10800,7 +10833,7 @@
     <row r="142">
       <c r="A142" s="11"/>
       <c r="B142" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C142" s="13"/>
@@ -10817,7 +10850,7 @@
     <row r="143">
       <c r="A143" s="11"/>
       <c r="B143" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C143" s="13"/>
@@ -10834,7 +10867,7 @@
     <row r="144">
       <c r="A144" s="11"/>
       <c r="B144" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C144" s="13"/>
@@ -10851,7 +10884,7 @@
     <row r="145">
       <c r="A145" s="11"/>
       <c r="B145" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C145" s="13"/>
@@ -10868,7 +10901,7 @@
     <row r="146">
       <c r="A146" s="11"/>
       <c r="B146" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C146" s="13"/>
@@ -10885,7 +10918,7 @@
     <row r="147">
       <c r="A147" s="11"/>
       <c r="B147" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C147" s="13"/>
@@ -10902,7 +10935,7 @@
     <row r="148">
       <c r="A148" s="11"/>
       <c r="B148" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C148" s="13"/>
@@ -10919,7 +10952,7 @@
     <row r="149">
       <c r="A149" s="11"/>
       <c r="B149" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C149" s="13"/>
@@ -10936,7 +10969,7 @@
     <row r="150">
       <c r="A150" s="11"/>
       <c r="B150" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C150" s="13"/>
@@ -10953,7 +10986,7 @@
     <row r="151">
       <c r="A151" s="11"/>
       <c r="B151" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C151" s="13"/>
@@ -10970,7 +11003,7 @@
     <row r="152">
       <c r="A152" s="11"/>
       <c r="B152" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C152" s="13"/>
@@ -10987,7 +11020,7 @@
     <row r="153">
       <c r="A153" s="11"/>
       <c r="B153" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C153" s="13"/>
@@ -11004,7 +11037,7 @@
     <row r="154">
       <c r="A154" s="11"/>
       <c r="B154" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C154" s="13"/>
@@ -11021,7 +11054,7 @@
     <row r="155">
       <c r="A155" s="11"/>
       <c r="B155" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C155" s="13"/>
@@ -11038,7 +11071,7 @@
     <row r="156">
       <c r="A156" s="11"/>
       <c r="B156" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C156" s="13"/>
@@ -11055,7 +11088,7 @@
     <row r="157">
       <c r="A157" s="11"/>
       <c r="B157" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C157" s="13"/>
@@ -11072,7 +11105,7 @@
     <row r="158">
       <c r="A158" s="11"/>
       <c r="B158" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C158" s="13"/>
@@ -11089,7 +11122,7 @@
     <row r="159">
       <c r="A159" s="11"/>
       <c r="B159" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C159" s="13"/>
@@ -11106,7 +11139,7 @@
     <row r="160">
       <c r="A160" s="11"/>
       <c r="B160" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C160" s="13"/>
@@ -11123,7 +11156,7 @@
     <row r="161">
       <c r="A161" s="11"/>
       <c r="B161" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C161" s="13"/>
@@ -11140,7 +11173,7 @@
     <row r="162">
       <c r="A162" s="11"/>
       <c r="B162" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C162" s="13"/>
@@ -11157,7 +11190,7 @@
     <row r="163">
       <c r="A163" s="11"/>
       <c r="B163" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C163" s="13"/>
@@ -11174,7 +11207,7 @@
     <row r="164">
       <c r="A164" s="11"/>
       <c r="B164" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C164" s="13"/>
@@ -11191,7 +11224,7 @@
     <row r="165">
       <c r="A165" s="11"/>
       <c r="B165" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C165" s="13"/>
@@ -11208,7 +11241,7 @@
     <row r="166">
       <c r="A166" s="11"/>
       <c r="B166" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C166" s="13"/>
@@ -11225,7 +11258,7 @@
     <row r="167">
       <c r="A167" s="11"/>
       <c r="B167" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C167" s="13"/>
@@ -11242,7 +11275,7 @@
     <row r="168">
       <c r="A168" s="11"/>
       <c r="B168" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C168" s="13"/>
@@ -11259,7 +11292,7 @@
     <row r="169">
       <c r="A169" s="11"/>
       <c r="B169" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C169" s="13"/>
@@ -11276,7 +11309,7 @@
     <row r="170">
       <c r="A170" s="11"/>
       <c r="B170" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C170" s="13"/>
@@ -11293,7 +11326,7 @@
     <row r="171">
       <c r="A171" s="11"/>
       <c r="B171" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C171" s="13"/>
@@ -11310,7 +11343,7 @@
     <row r="172">
       <c r="A172" s="11"/>
       <c r="B172" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C172" s="13"/>
@@ -11327,7 +11360,7 @@
     <row r="173">
       <c r="A173" s="11"/>
       <c r="B173" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C173" s="13"/>
@@ -11344,7 +11377,7 @@
     <row r="174">
       <c r="A174" s="11"/>
       <c r="B174" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C174" s="13"/>
@@ -11361,7 +11394,7 @@
     <row r="175">
       <c r="A175" s="11"/>
       <c r="B175" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C175" s="13"/>
@@ -11378,7 +11411,7 @@
     <row r="176">
       <c r="A176" s="11"/>
       <c r="B176" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C176" s="13"/>
@@ -11395,7 +11428,7 @@
     <row r="177">
       <c r="A177" s="11"/>
       <c r="B177" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C177" s="13"/>
@@ -11412,7 +11445,7 @@
     <row r="178">
       <c r="A178" s="11"/>
       <c r="B178" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C178" s="13"/>
@@ -11429,7 +11462,7 @@
     <row r="179">
       <c r="A179" s="11"/>
       <c r="B179" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C179" s="13"/>
@@ -11446,7 +11479,7 @@
     <row r="180">
       <c r="A180" s="11"/>
       <c r="B180" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C180" s="13"/>
@@ -11463,7 +11496,7 @@
     <row r="181">
       <c r="A181" s="11"/>
       <c r="B181" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C181" s="13"/>
@@ -11480,7 +11513,7 @@
     <row r="182">
       <c r="A182" s="11"/>
       <c r="B182" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C182" s="13"/>
@@ -11497,7 +11530,7 @@
     <row r="183">
       <c r="A183" s="11"/>
       <c r="B183" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C183" s="13"/>
@@ -11514,7 +11547,7 @@
     <row r="184">
       <c r="A184" s="11"/>
       <c r="B184" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C184" s="13"/>
@@ -11531,7 +11564,7 @@
     <row r="185">
       <c r="A185" s="11"/>
       <c r="B185" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C185" s="13"/>
@@ -11548,7 +11581,7 @@
     <row r="186">
       <c r="A186" s="11"/>
       <c r="B186" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C186" s="13"/>
@@ -11565,7 +11598,7 @@
     <row r="187">
       <c r="A187" s="11"/>
       <c r="B187" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C187" s="13"/>
@@ -11582,7 +11615,7 @@
     <row r="188">
       <c r="A188" s="11"/>
       <c r="B188" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C188" s="13"/>
@@ -11599,7 +11632,7 @@
     <row r="189">
       <c r="A189" s="11"/>
       <c r="B189" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C189" s="13"/>
@@ -11616,7 +11649,7 @@
     <row r="190">
       <c r="A190" s="11"/>
       <c r="B190" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C190" s="13"/>
@@ -11633,7 +11666,7 @@
     <row r="191">
       <c r="A191" s="11"/>
       <c r="B191" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C191" s="13"/>
@@ -11650,7 +11683,7 @@
     <row r="192">
       <c r="A192" s="11"/>
       <c r="B192" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C192" s="13"/>
@@ -11667,7 +11700,7 @@
     <row r="193">
       <c r="A193" s="11"/>
       <c r="B193" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C193" s="13"/>
@@ -11684,7 +11717,7 @@
     <row r="194">
       <c r="A194" s="11"/>
       <c r="B194" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C194" s="13"/>
@@ -11701,7 +11734,7 @@
     <row r="195">
       <c r="A195" s="11"/>
       <c r="B195" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C195" s="13"/>
@@ -11718,7 +11751,7 @@
     <row r="196">
       <c r="A196" s="11"/>
       <c r="B196" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C196" s="13"/>
@@ -11735,7 +11768,7 @@
     <row r="197">
       <c r="A197" s="11"/>
       <c r="B197" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C197" s="13"/>
@@ -11752,7 +11785,7 @@
     <row r="198">
       <c r="A198" s="11"/>
       <c r="B198" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C198" s="13"/>
@@ -11769,7 +11802,7 @@
     <row r="199">
       <c r="A199" s="11"/>
       <c r="B199" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="C199" s="13"/>
@@ -11786,7 +11819,7 @@
     <row r="200">
       <c r="A200" s="11"/>
       <c r="B200" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="B200:B263" si="3">IF($G200="","-",CONCATENATE(F200," ",G200," ",H200," ",I200," ",K200," ",L200))</f>
         <v>-</v>
       </c>
       <c r="C200" s="13"/>
@@ -11803,7 +11836,7 @@
     <row r="201">
       <c r="A201" s="11"/>
       <c r="B201" s="12" t="str">
-        <f t="shared" ref="B201:B264" si="4">IF($G201="","-",CONCATENATE(F201," ",G201," ",H201," ",I201," ",K201," ",L201))</f>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C201" s="13"/>
@@ -11820,7 +11853,7 @@
     <row r="202">
       <c r="A202" s="11"/>
       <c r="B202" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C202" s="13"/>
@@ -11837,7 +11870,7 @@
     <row r="203">
       <c r="A203" s="11"/>
       <c r="B203" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C203" s="13"/>
@@ -11854,7 +11887,7 @@
     <row r="204">
       <c r="A204" s="11"/>
       <c r="B204" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C204" s="13"/>
@@ -11871,7 +11904,7 @@
     <row r="205">
       <c r="A205" s="11"/>
       <c r="B205" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C205" s="13"/>
@@ -11888,7 +11921,7 @@
     <row r="206">
       <c r="A206" s="11"/>
       <c r="B206" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C206" s="13"/>
@@ -11905,7 +11938,7 @@
     <row r="207">
       <c r="A207" s="11"/>
       <c r="B207" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C207" s="13"/>
@@ -11922,7 +11955,7 @@
     <row r="208">
       <c r="A208" s="11"/>
       <c r="B208" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C208" s="13"/>
@@ -11939,7 +11972,7 @@
     <row r="209">
       <c r="A209" s="11"/>
       <c r="B209" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C209" s="13"/>
@@ -11956,7 +11989,7 @@
     <row r="210">
       <c r="A210" s="11"/>
       <c r="B210" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C210" s="13"/>
@@ -11973,7 +12006,7 @@
     <row r="211">
       <c r="A211" s="11"/>
       <c r="B211" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C211" s="13"/>
@@ -11990,7 +12023,7 @@
     <row r="212">
       <c r="A212" s="11"/>
       <c r="B212" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C212" s="13"/>
@@ -12007,7 +12040,7 @@
     <row r="213">
       <c r="A213" s="11"/>
       <c r="B213" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C213" s="13"/>
@@ -12024,7 +12057,7 @@
     <row r="214">
       <c r="A214" s="11"/>
       <c r="B214" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C214" s="13"/>
@@ -12041,7 +12074,7 @@
     <row r="215">
       <c r="A215" s="11"/>
       <c r="B215" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C215" s="13"/>
@@ -12058,7 +12091,7 @@
     <row r="216">
       <c r="A216" s="11"/>
       <c r="B216" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C216" s="13"/>
@@ -12075,7 +12108,7 @@
     <row r="217">
       <c r="A217" s="11"/>
       <c r="B217" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C217" s="13"/>
@@ -12092,7 +12125,7 @@
     <row r="218">
       <c r="A218" s="11"/>
       <c r="B218" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C218" s="13"/>
@@ -12109,7 +12142,7 @@
     <row r="219">
       <c r="A219" s="11"/>
       <c r="B219" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C219" s="13"/>
@@ -12126,7 +12159,7 @@
     <row r="220">
       <c r="A220" s="11"/>
       <c r="B220" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C220" s="13"/>
@@ -12143,7 +12176,7 @@
     <row r="221">
       <c r="A221" s="11"/>
       <c r="B221" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C221" s="13"/>
@@ -12160,7 +12193,7 @@
     <row r="222">
       <c r="A222" s="11"/>
       <c r="B222" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C222" s="13"/>
@@ -12177,7 +12210,7 @@
     <row r="223">
       <c r="A223" s="11"/>
       <c r="B223" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C223" s="13"/>
@@ -12194,7 +12227,7 @@
     <row r="224">
       <c r="A224" s="11"/>
       <c r="B224" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C224" s="13"/>
@@ -12211,7 +12244,7 @@
     <row r="225">
       <c r="A225" s="11"/>
       <c r="B225" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C225" s="13"/>
@@ -12228,7 +12261,7 @@
     <row r="226">
       <c r="A226" s="11"/>
       <c r="B226" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C226" s="13"/>
@@ -12245,7 +12278,7 @@
     <row r="227">
       <c r="A227" s="11"/>
       <c r="B227" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C227" s="13"/>
@@ -12262,7 +12295,7 @@
     <row r="228">
       <c r="A228" s="11"/>
       <c r="B228" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C228" s="13"/>
@@ -12279,7 +12312,7 @@
     <row r="229">
       <c r="A229" s="11"/>
       <c r="B229" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C229" s="13"/>
@@ -12296,7 +12329,7 @@
     <row r="230">
       <c r="A230" s="11"/>
       <c r="B230" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C230" s="13"/>
@@ -12313,7 +12346,7 @@
     <row r="231">
       <c r="A231" s="11"/>
       <c r="B231" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C231" s="13"/>
@@ -12330,7 +12363,7 @@
     <row r="232">
       <c r="A232" s="11"/>
       <c r="B232" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C232" s="13"/>
@@ -12347,7 +12380,7 @@
     <row r="233">
       <c r="A233" s="11"/>
       <c r="B233" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C233" s="13"/>
@@ -12364,7 +12397,7 @@
     <row r="234">
       <c r="A234" s="11"/>
       <c r="B234" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C234" s="13"/>
@@ -12381,7 +12414,7 @@
     <row r="235">
       <c r="A235" s="11"/>
       <c r="B235" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C235" s="13"/>
@@ -12398,7 +12431,7 @@
     <row r="236">
       <c r="A236" s="11"/>
       <c r="B236" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C236" s="13"/>
@@ -12415,7 +12448,7 @@
     <row r="237">
       <c r="A237" s="11"/>
       <c r="B237" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C237" s="13"/>
@@ -12432,7 +12465,7 @@
     <row r="238">
       <c r="A238" s="11"/>
       <c r="B238" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C238" s="13"/>
@@ -12449,7 +12482,7 @@
     <row r="239">
       <c r="A239" s="11"/>
       <c r="B239" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C239" s="13"/>
@@ -12466,7 +12499,7 @@
     <row r="240">
       <c r="A240" s="11"/>
       <c r="B240" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C240" s="13"/>
@@ -12483,7 +12516,7 @@
     <row r="241">
       <c r="A241" s="11"/>
       <c r="B241" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C241" s="13"/>
@@ -12500,7 +12533,7 @@
     <row r="242">
       <c r="A242" s="11"/>
       <c r="B242" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C242" s="13"/>
@@ -12517,7 +12550,7 @@
     <row r="243">
       <c r="A243" s="11"/>
       <c r="B243" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C243" s="13"/>
@@ -12534,7 +12567,7 @@
     <row r="244">
       <c r="A244" s="11"/>
       <c r="B244" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C244" s="13"/>
@@ -12551,7 +12584,7 @@
     <row r="245">
       <c r="A245" s="11"/>
       <c r="B245" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C245" s="13"/>
@@ -12568,7 +12601,7 @@
     <row r="246">
       <c r="A246" s="11"/>
       <c r="B246" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C246" s="13"/>
@@ -12585,7 +12618,7 @@
     <row r="247">
       <c r="A247" s="11"/>
       <c r="B247" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C247" s="13"/>
@@ -12602,7 +12635,7 @@
     <row r="248">
       <c r="A248" s="11"/>
       <c r="B248" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C248" s="13"/>
@@ -12619,7 +12652,7 @@
     <row r="249">
       <c r="A249" s="11"/>
       <c r="B249" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C249" s="13"/>
@@ -12636,7 +12669,7 @@
     <row r="250">
       <c r="A250" s="11"/>
       <c r="B250" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C250" s="13"/>
@@ -12653,7 +12686,7 @@
     <row r="251">
       <c r="A251" s="11"/>
       <c r="B251" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C251" s="13"/>
@@ -12670,7 +12703,7 @@
     <row r="252">
       <c r="A252" s="11"/>
       <c r="B252" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C252" s="13"/>
@@ -12687,7 +12720,7 @@
     <row r="253">
       <c r="A253" s="11"/>
       <c r="B253" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C253" s="13"/>
@@ -12704,7 +12737,7 @@
     <row r="254">
       <c r="A254" s="11"/>
       <c r="B254" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C254" s="13"/>
@@ -12721,7 +12754,7 @@
     <row r="255">
       <c r="A255" s="11"/>
       <c r="B255" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C255" s="13"/>
@@ -12738,7 +12771,7 @@
     <row r="256">
       <c r="A256" s="11"/>
       <c r="B256" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C256" s="13"/>
@@ -12755,7 +12788,7 @@
     <row r="257">
       <c r="A257" s="11"/>
       <c r="B257" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C257" s="13"/>
@@ -12772,7 +12805,7 @@
     <row r="258">
       <c r="A258" s="11"/>
       <c r="B258" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C258" s="13"/>
@@ -12789,7 +12822,7 @@
     <row r="259">
       <c r="A259" s="11"/>
       <c r="B259" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C259" s="13"/>
@@ -12806,7 +12839,7 @@
     <row r="260">
       <c r="A260" s="11"/>
       <c r="B260" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C260" s="13"/>
@@ -12823,7 +12856,7 @@
     <row r="261">
       <c r="A261" s="11"/>
       <c r="B261" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C261" s="13"/>
@@ -12840,7 +12873,7 @@
     <row r="262">
       <c r="A262" s="11"/>
       <c r="B262" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C262" s="13"/>
@@ -12857,7 +12890,7 @@
     <row r="263">
       <c r="A263" s="11"/>
       <c r="B263" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="C263" s="13"/>
@@ -12874,7 +12907,7 @@
     <row r="264">
       <c r="A264" s="11"/>
       <c r="B264" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="B264:B288" si="4">IF($G264="","-",CONCATENATE(F264," ",G264," ",H264," ",I264," ",K264," ",L264))</f>
         <v>-</v>
       </c>
       <c r="C264" s="13"/>
@@ -12891,7 +12924,7 @@
     <row r="265">
       <c r="A265" s="11"/>
       <c r="B265" s="12" t="str">
-        <f t="shared" ref="B265:B288" si="5">IF($G265="","-",CONCATENATE(F265," ",G265," ",H265," ",I265," ",K265," ",L265))</f>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C265" s="13"/>
@@ -12908,7 +12941,7 @@
     <row r="266">
       <c r="A266" s="11"/>
       <c r="B266" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C266" s="13"/>
@@ -12925,7 +12958,7 @@
     <row r="267">
       <c r="A267" s="11"/>
       <c r="B267" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C267" s="13"/>
@@ -12942,7 +12975,7 @@
     <row r="268">
       <c r="A268" s="11"/>
       <c r="B268" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C268" s="13"/>
@@ -12959,7 +12992,7 @@
     <row r="269">
       <c r="A269" s="11"/>
       <c r="B269" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C269" s="13"/>
@@ -12976,7 +13009,7 @@
     <row r="270">
       <c r="A270" s="11"/>
       <c r="B270" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C270" s="13"/>
@@ -12993,7 +13026,7 @@
     <row r="271">
       <c r="A271" s="11"/>
       <c r="B271" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C271" s="13"/>
@@ -13010,7 +13043,7 @@
     <row r="272">
       <c r="A272" s="11"/>
       <c r="B272" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C272" s="13"/>
@@ -13027,7 +13060,7 @@
     <row r="273">
       <c r="A273" s="11"/>
       <c r="B273" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C273" s="13"/>
@@ -13044,7 +13077,7 @@
     <row r="274">
       <c r="A274" s="11"/>
       <c r="B274" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C274" s="13"/>
@@ -13061,7 +13094,7 @@
     <row r="275">
       <c r="A275" s="11"/>
       <c r="B275" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C275" s="13"/>
@@ -13078,7 +13111,7 @@
     <row r="276">
       <c r="A276" s="11"/>
       <c r="B276" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C276" s="13"/>
@@ -13095,7 +13128,7 @@
     <row r="277">
       <c r="A277" s="11"/>
       <c r="B277" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C277" s="13"/>
@@ -13112,7 +13145,7 @@
     <row r="278">
       <c r="A278" s="11"/>
       <c r="B278" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C278" s="13"/>
@@ -13129,7 +13162,7 @@
     <row r="279">
       <c r="A279" s="11"/>
       <c r="B279" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C279" s="13"/>
@@ -13146,7 +13179,7 @@
     <row r="280">
       <c r="A280" s="11"/>
       <c r="B280" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C280" s="13"/>
@@ -13163,7 +13196,7 @@
     <row r="281">
       <c r="A281" s="11"/>
       <c r="B281" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C281" s="13"/>
@@ -13180,7 +13213,7 @@
     <row r="282">
       <c r="A282" s="11"/>
       <c r="B282" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C282" s="13"/>
@@ -13197,7 +13230,7 @@
     <row r="283">
       <c r="A283" s="11"/>
       <c r="B283" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C283" s="13"/>
@@ -13214,7 +13247,7 @@
     <row r="284">
       <c r="A284" s="11"/>
       <c r="B284" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C284" s="13"/>
@@ -13231,7 +13264,7 @@
     <row r="285">
       <c r="A285" s="11"/>
       <c r="B285" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C285" s="13"/>
@@ -13248,7 +13281,7 @@
     <row r="286">
       <c r="A286" s="11"/>
       <c r="B286" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C286" s="13"/>
@@ -13265,7 +13298,7 @@
     <row r="287">
       <c r="A287" s="11"/>
       <c r="B287" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="C287" s="13"/>
@@ -13281,38 +13314,38 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B288" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">END END END END END END</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K288" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -13343,7 +13376,7 @@
   <sheetData>
     <row r="4" ht="33">
       <c r="A4" s="18" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -13356,21 +13389,21 @@
     </row>
     <row r="6" ht="15.75">
       <c r="A6" s="16" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" ht="15.75">
       <c r="A7" s="19" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="23"/>
@@ -13381,22 +13414,22 @@
     <row r="8" ht="15.75">
       <c r="A8" s="25"/>
       <c r="B8" s="20" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" ht="15.75">
       <c r="A9" s="28"/>
       <c r="B9" s="20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D9" s="29">
         <v>46120</v>
@@ -13408,25 +13441,25 @@
     </row>
     <row r="11" ht="15.75">
       <c r="A11" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>226</v>
-      </c>
       <c r="D11" s="30" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" ht="15.75">
       <c r="A12" s="28"/>
       <c r="B12" s="20" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D12" s="29">
         <v>46196</v>
@@ -13438,13 +13471,13 @@
     </row>
     <row r="14" ht="15.75">
       <c r="A14" s="19" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D14" s="29">
         <v>46195</v>
@@ -13453,10 +13486,10 @@
     <row r="15" ht="15.75">
       <c r="A15" s="25"/>
       <c r="B15" s="20" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D15" s="30">
         <v>2</v>
@@ -13465,10 +13498,10 @@
     <row r="16" ht="15.75">
       <c r="A16" s="28"/>
       <c r="B16" s="31" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D16" s="32" t="str">
         <f>CONCATENATE("MT-",TEXT(D14,"yyyy"),TEXT(D14,"mm"),TEXT(D14,"dd"),IF(LEN(D15)&lt;2,"0"&amp;D15&amp;"호",D15&amp;"호"))</f>
@@ -13481,25 +13514,25 @@
     </row>
     <row r="18" ht="15.75">
       <c r="A18" s="19" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" ht="15.75">
       <c r="A19" s="25"/>
       <c r="B19" s="20" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D19" s="30">
         <v>6108524413</v>
@@ -13508,25 +13541,25 @@
     <row r="20" ht="15.75">
       <c r="A20" s="25"/>
       <c r="B20" s="33" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" ht="15.75">
       <c r="A21" s="28"/>
       <c r="B21" s="33" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22">
@@ -13535,13 +13568,13 @@
     </row>
     <row r="23" ht="15.75">
       <c r="A23" s="34" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B23" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="C23" s="33" t="s">
         <v>250</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>245</v>
       </c>
       <c r="D23" s="33">
         <v>1</v>
@@ -13551,55 +13584,55 @@
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
       <c r="J24" s="35" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K24" s="36"/>
       <c r="L24" s="37"/>
       <c r="M24" s="38" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" ht="15.75">
       <c r="A25" s="34" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>2</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="H25" s="39" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K25" s="40" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="L25" s="40" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="M25" s="41" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" ht="15.75">
       <c r="B26" s="42" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C26" s="30">
         <v>1</v>
@@ -13619,7 +13652,7 @@
         <v>28</v>
       </c>
       <c r="H26" s="46">
-        <f t="shared" ref="H26:H35" si="6">E26*G26</f>
+        <f t="shared" ref="H26:H35" si="5">E26*G26</f>
         <v>82600000</v>
       </c>
       <c r="J26" s="47" t="str">
@@ -13635,88 +13668,121 @@
         <v>투광조명</v>
       </c>
       <c r="M26" s="30" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" ht="15.75">
       <c r="C27" s="30">
         <v>2</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="49"/>
+      <c r="D27" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="43">
+        <f>IF(D26="","-",VLOOKUP($D26,데이터!$A$8:$K$287,3,0))</f>
+        <v>2950000</v>
+      </c>
+      <c r="F27" s="48" t="str">
+        <f>IF(E26="","-",VLOOKUP($D26,데이터!$A$8:$K$287,10,0))</f>
+        <v>개</v>
+      </c>
+      <c r="G27" s="49">
+        <v>28</v>
+      </c>
       <c r="H27" s="46">
-        <v>0</v>
+        <f>E27*G27</f>
+        <v>82600000</v>
       </c>
       <c r="J27" s="47" t="str">
         <f>IF($D27="","",VLOOKUP($D27,데이터!$A$8:$K$287,4,0))</f>
-        <v/>
+        <v>39111611</v>
       </c>
       <c r="K27" s="47" t="str">
         <f>IF($D27="","",VLOOKUP($D27,데이터!$A$8:$K$287,2,0))</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="L27" s="47" t="str">
         <f>IF($D27="","",VLOOKUP($D27,데이터!$A$8:$K$287,5,0))</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="M27" s="30" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" ht="15.75">
       <c r="C28" s="30">
         <v>3</v>
       </c>
-      <c r="D28" s="30"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="50"/>
+      <c r="D28" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="43">
+        <f>IF(D26="","-",VLOOKUP($D26,데이터!$A$8:$K$287,3,0))</f>
+        <v>2950000</v>
+      </c>
+      <c r="F28" s="45" t="str">
+        <f>IF(E26="","-",VLOOKUP($D26,데이터!$A$8:$K$287,10,0))</f>
+        <v>개</v>
+      </c>
+      <c r="G28" s="50">
+        <v>28</v>
+      </c>
       <c r="H28" s="46">
-        <v>0</v>
+        <f>E28*G28</f>
+        <v>82600000</v>
       </c>
       <c r="J28" s="47" t="str">
         <f>IF($D28="","",VLOOKUP($D28,데이터!$A$8:$K$287,4,0))</f>
-        <v/>
+        <v>39111611</v>
       </c>
       <c r="K28" s="47" t="str">
         <f>IF($D28="","",VLOOKUP($D28,데이터!$A$8:$K$287,2,0))</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="L28" s="47" t="str">
         <f>IF($D28="","",VLOOKUP($D28,데이터!$A$8:$K$287,5,0))</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="M28" s="30" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" ht="15.75">
       <c r="C29" s="30">
         <v>4</v>
       </c>
-      <c r="D29" s="30"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="50"/>
+      <c r="D29" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="43">
+        <f>IF(D26="","-",VLOOKUP($D26,데이터!$A$8:$K$287,3,0))</f>
+        <v>2950000</v>
+      </c>
+      <c r="F29" s="45" t="str">
+        <f>IF(E26="","-",VLOOKUP($D26,데이터!$A$8:$K$287,10,0))</f>
+        <v>개</v>
+      </c>
+      <c r="G29" s="50">
+        <v>28</v>
+      </c>
       <c r="H29" s="46">
-        <v>0</v>
+        <f>E29*G29</f>
+        <v>82600000</v>
       </c>
       <c r="J29" s="47" t="str">
         <f>IF($D29="","",VLOOKUP($D29,데이터!$A$8:$K$287,4,0))</f>
-        <v/>
+        <v>39111611</v>
       </c>
       <c r="K29" s="47" t="str">
         <f>IF($D29="","",VLOOKUP($D29,데이터!$A$8:$K$287,2,0))</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="L29" s="47" t="str">
         <f>IF($D29="","",VLOOKUP($D29,데이터!$A$8:$K$287,5,0))</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="M29" s="30" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" ht="15.75">
@@ -13728,7 +13794,7 @@
       <c r="F30" s="45"/>
       <c r="G30" s="50"/>
       <c r="H30" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J30" s="30"/>
@@ -13745,7 +13811,7 @@
       <c r="F31" s="45"/>
       <c r="G31" s="50"/>
       <c r="H31" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J31" s="30"/>
@@ -13762,7 +13828,7 @@
       <c r="F32" s="45"/>
       <c r="G32" s="52"/>
       <c r="H32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J32" s="30"/>
@@ -13779,7 +13845,7 @@
       <c r="F33" s="45"/>
       <c r="G33" s="50"/>
       <c r="H33" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J33" s="30"/>
@@ -13796,7 +13862,7 @@
       <c r="F34" s="45"/>
       <c r="G34" s="50"/>
       <c r="H34" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J34" s="30"/>
@@ -13813,7 +13879,7 @@
       <c r="F35" s="45"/>
       <c r="G35" s="50"/>
       <c r="H35" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J35" s="30"/>
@@ -13823,29 +13889,29 @@
     </row>
     <row r="36" ht="15.75">
       <c r="C36" s="53" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D36" s="53"/>
       <c r="E36" s="54"/>
       <c r="F36" s="55"/>
       <c r="G36" s="56">
         <f>SUM(G26:G35)</f>
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H36" s="57">
         <f>SUM(H26:H35)</f>
-        <v>82600000</v>
+        <v>330400000</v>
       </c>
     </row>
     <row r="38" ht="15.75">
       <c r="A38" s="34" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D38" s="51">
         <v>446040</v>
@@ -13865,10 +13931,10 @@
     </row>
     <row r="45" ht="15.75">
       <c r="B45" s="58" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C45" s="58" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D45" s="51">
         <f>$D$38</f>
@@ -13887,19 +13953,19 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{005E006F-007A-405F-A51B-009E000D007E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00FD00AD-003D-499A-B508-0040001F0083}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"유, 무"</xm:f>
           </x14:formula1>
           <xm:sqref>D21</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{006C0051-008C-4DE3-8D4F-001A007C0072}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00C10080-007C-42D7-8373-0011005900D5}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"청, 기관, 교,  사업소"</xm:f>
           </x14:formula1>
           <xm:sqref>D20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{005C009B-00B9-4AFC-A379-000E002A0024}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D100C9-0009-48CC-907E-003700730045}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1,2,3"</xm:f>
           </x14:formula1>
@@ -13925,7 +13991,7 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1">
       <c r="A1" s="59" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B1" s="59"/>
       <c r="C1" s="59"/>
@@ -13941,7 +14007,7 @@
     </row>
     <row r="2" ht="53.25" customHeight="1">
       <c r="A2" s="60" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B2" s="60"/>
       <c r="C2" s="60"/>
@@ -13971,7 +14037,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="15" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B4" s="16" t="str">
         <f>'기초 자료 입력'!D18</f>
@@ -13990,7 +14056,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="15" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -14006,7 +14072,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="15" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B6" s="16" t="str">
         <f>'기초 자료 입력'!D7&amp;" 건의 납품계 제출"</f>
@@ -14073,7 +14139,7 @@
     </row>
     <row r="10" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -14120,7 +14186,7 @@
     </row>
     <row r="13" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="66" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66" t="str">
@@ -14139,7 +14205,7 @@
     </row>
     <row r="14" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="15" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="67">
@@ -14158,7 +14224,7 @@
     </row>
     <row r="15" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="67">
@@ -14191,7 +14257,7 @@
     </row>
     <row r="17" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -14305,7 +14371,7 @@
     </row>
     <row r="25" ht="25.5" customHeight="1">
       <c r="A25" s="68" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B25" s="68"/>
       <c r="C25" s="68"/>
@@ -14377,7 +14443,7 @@
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="72" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B30" s="72"/>
       <c r="C30" s="72"/>
@@ -14393,7 +14459,7 @@
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="72" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B31" s="73"/>
       <c r="C31" s="73"/>
@@ -14409,7 +14475,7 @@
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="72" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B32" s="72"/>
       <c r="C32" s="72" t="str">
@@ -14420,7 +14486,7 @@
       <c r="E32" s="72"/>
       <c r="F32" s="73"/>
       <c r="G32" s="72" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H32" s="73"/>
       <c r="I32" s="73"/>
@@ -14430,16 +14496,16 @@
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="73" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B33" s="73"/>
       <c r="C33" s="73" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F33" s="73"/>
       <c r="G33" s="73"/>
       <c r="I33" s="73" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="J33" s="73"/>
       <c r="K33" s="73"/>
@@ -14447,18 +14513,18 @@
     </row>
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="72" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B34" s="72"/>
       <c r="C34" s="72"/>
       <c r="D34" s="72" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E34" s="72"/>
       <c r="F34" s="72"/>
       <c r="G34" s="72"/>
       <c r="H34" s="72" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I34" s="72"/>
       <c r="J34" s="72"/>
@@ -15488,7 +15554,7 @@
     <row r="1" ht="24" customHeight="1"/>
     <row r="2" ht="55.5" customHeight="1">
       <c r="A2" s="75" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B2" s="75"/>
       <c r="C2" s="75"/>
@@ -15498,7 +15564,7 @@
     </row>
     <row r="3" ht="27" customHeight="1">
       <c r="D3" s="76" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E3" s="76"/>
       <c r="F3" s="77"/>
@@ -15543,7 +15609,7 @@
     </row>
     <row r="11" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="74" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B11" s="78" t="str">
         <f>'기초 자료 입력'!$D$11</f>
@@ -15557,7 +15623,7 @@
     </row>
     <row r="12" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="74" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B12" s="80" t="str">
         <f>'기초 자료 입력'!$D$7</f>
@@ -15571,7 +15637,7 @@
     </row>
     <row r="13" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="74" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B13" s="78" t="str">
         <f>공문!$C$13</f>
@@ -15584,7 +15650,7 @@
     </row>
     <row r="14" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="74" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B14" s="81">
         <f>'기초 자료 입력'!$D$9</f>
@@ -15597,7 +15663,7 @@
     </row>
     <row r="15" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="74" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B15" s="81">
         <f>'기초 자료 입력'!$D$12</f>
@@ -15610,7 +15676,7 @@
     </row>
     <row r="16" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="74" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B16" s="81">
         <f>'기초 자료 입력'!$D$14</f>
@@ -15630,7 +15696,7 @@
     </row>
     <row r="18" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="79" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B18" s="79"/>
       <c r="C18" s="79"/>
@@ -15656,7 +15722,7 @@
     </row>
     <row r="21" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="78" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B21" s="78"/>
       <c r="C21" s="78"/>
@@ -15666,7 +15732,7 @@
     </row>
     <row r="22" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="78" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B22" s="78"/>
       <c r="C22" s="78"/>
@@ -15676,7 +15742,7 @@
     </row>
     <row r="23" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="78" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B23" s="78"/>
       <c r="C23" s="78"/>
@@ -15686,7 +15752,7 @@
     </row>
     <row r="24" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="78" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B24" s="78"/>
       <c r="C24" s="78"/>
@@ -15730,7 +15796,7 @@
       <c r="F28" s="78"/>
       <c r="H28" s="74"/>
       <c r="J28" s="78" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K28" s="78"/>
       <c r="L28" s="78"/>
@@ -15740,14 +15806,14 @@
       <c r="A29" s="74"/>
       <c r="B29" s="74"/>
       <c r="C29" s="78" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D29" s="74"/>
       <c r="E29" s="74"/>
       <c r="F29" s="74"/>
       <c r="H29" s="74"/>
       <c r="J29" s="78" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K29" s="78"/>
       <c r="L29" s="78"/>
@@ -15757,16 +15823,16 @@
       <c r="A30" s="74"/>
       <c r="B30" s="74"/>
       <c r="C30" s="83" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D30" s="78" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E30" s="78"/>
       <c r="F30" s="74"/>
       <c r="H30" s="74"/>
       <c r="J30" s="78" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K30" s="78"/>
       <c r="L30" s="78"/>
@@ -15776,16 +15842,16 @@
       <c r="A31" s="74"/>
       <c r="B31" s="74"/>
       <c r="C31" s="83" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D31" s="78" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E31" s="78"/>
       <c r="F31" s="74"/>
       <c r="H31" s="74"/>
       <c r="J31" s="78" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K31" s="78"/>
       <c r="L31" s="78"/>
@@ -15795,13 +15861,13 @@
       <c r="A32" s="74"/>
       <c r="B32" s="74"/>
       <c r="C32" s="83" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D32" s="78" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E32" s="78" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F32" s="74"/>
     </row>
@@ -15907,7 +15973,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="86" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B2" s="87"/>
       <c r="C2" s="87"/>
@@ -15945,7 +16011,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="90" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B4" s="91"/>
       <c r="C4" s="92"/>
@@ -15965,7 +16031,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="96" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B5" s="97"/>
       <c r="C5" s="98" t="str">
@@ -15974,7 +16040,7 @@
       </c>
       <c r="D5" s="99"/>
       <c r="E5" s="92" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F5" s="100"/>
       <c r="G5" s="100"/>
@@ -15984,7 +16050,7 @@
         <v>R26TB01782064-00</v>
       </c>
       <c r="J5" s="92" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K5" s="100"/>
       <c r="L5" s="91"/>
@@ -15998,7 +16064,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="96" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B6" s="97"/>
       <c r="C6" s="105" t="str">
@@ -16007,7 +16073,7 @@
       </c>
       <c r="D6" s="106"/>
       <c r="E6" s="107" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F6" s="108"/>
       <c r="G6" s="108"/>
@@ -16017,7 +16083,7 @@
         <v xml:space="preserve">2026. 04. 08.</v>
       </c>
       <c r="J6" s="107" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K6" s="108"/>
       <c r="L6" s="97"/>
@@ -16028,7 +16094,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="96" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B7" s="97"/>
       <c r="C7" s="113" t="str">
@@ -16037,7 +16103,7 @@
       </c>
       <c r="D7" s="99"/>
       <c r="E7" s="107" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F7" s="108"/>
       <c r="G7" s="108"/>
@@ -16047,7 +16113,7 @@
         <v>6108524413</v>
       </c>
       <c r="J7" s="107" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="K7" s="108"/>
       <c r="L7" s="97"/>
@@ -16058,23 +16124,23 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="115" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B8" s="116"/>
       <c r="C8" s="117">
         <f>J41</f>
-        <v>82599999.999999985</v>
+        <v>247799999.99999997</v>
       </c>
       <c r="D8" s="106"/>
       <c r="E8" s="107" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F8" s="108"/>
       <c r="G8" s="108"/>
       <c r="H8" s="97"/>
       <c r="I8" s="114"/>
       <c r="J8" s="107" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="K8" s="108"/>
       <c r="L8" s="97"/>
@@ -16085,26 +16151,26 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="96" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B9" s="97"/>
       <c r="C9" s="110"/>
       <c r="D9" s="106"/>
       <c r="E9" s="107" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="F9" s="108"/>
       <c r="G9" s="108"/>
       <c r="H9" s="97"/>
       <c r="I9" s="114"/>
       <c r="J9" s="107" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="K9" s="108"/>
       <c r="L9" s="97"/>
       <c r="M9" s="117">
         <f>J41</f>
-        <v>82599999.999999985</v>
+        <v>247799999.99999997</v>
       </c>
       <c r="N9" s="111"/>
       <c r="O9" s="111"/>
@@ -16112,16 +16178,16 @@
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="118" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B10" s="119"/>
       <c r="C10" s="120">
         <f>J41</f>
-        <v>82599999.999999985</v>
+        <v>247799999.99999997</v>
       </c>
       <c r="D10" s="121"/>
       <c r="E10" s="122" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F10" s="123"/>
       <c r="G10" s="123"/>
@@ -16131,13 +16197,13 @@
         <v>446040</v>
       </c>
       <c r="J10" s="122" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K10" s="123"/>
       <c r="L10" s="119"/>
       <c r="M10" s="120">
         <f>SUM(C10,I10)</f>
-        <v>83046039.999999985</v>
+        <v>248246039.99999997</v>
       </c>
       <c r="N10" s="125"/>
       <c r="O10" s="125"/>
@@ -16145,7 +16211,7 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="127" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B11" s="106"/>
       <c r="C11" s="110"/>
@@ -16155,7 +16221,7 @@
       <c r="G11" s="128"/>
       <c r="H11" s="121"/>
       <c r="I11" s="129" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J11" s="128"/>
       <c r="K11" s="125"/>
@@ -16203,7 +16269,7 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="141" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B14" s="142"/>
       <c r="C14" s="142"/>
@@ -16213,7 +16279,7 @@
       <c r="G14" s="142"/>
       <c r="H14" s="143"/>
       <c r="I14" s="144" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J14" s="142"/>
       <c r="K14" s="142"/>
@@ -16225,7 +16291,7 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="141" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B15" s="142"/>
       <c r="C15" s="142"/>
@@ -16256,7 +16322,7 @@
       <c r="G16" s="151"/>
       <c r="H16" s="152"/>
       <c r="I16" s="153" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J16" s="154">
         <f>C16</f>
@@ -16271,7 +16337,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="156" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B17" s="157"/>
       <c r="C17" s="157"/>
@@ -16291,7 +16357,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="162" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B18" s="163"/>
       <c r="C18" s="163"/>
@@ -16301,10 +16367,10 @@
       <c r="G18" s="163"/>
       <c r="H18" s="164"/>
       <c r="I18" s="165" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J18" s="166" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K18" s="166"/>
       <c r="L18" s="166"/>
@@ -16323,7 +16389,7 @@
       <c r="G19" s="163"/>
       <c r="H19" s="164"/>
       <c r="I19" s="165" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J19" s="168"/>
       <c r="K19" s="168"/>
@@ -16335,7 +16401,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="162" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B20" s="163"/>
       <c r="C20" s="163"/>
@@ -16345,10 +16411,10 @@
       <c r="G20" s="163"/>
       <c r="H20" s="164"/>
       <c r="I20" s="165" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J20" s="166" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K20" s="166"/>
       <c r="L20" s="166"/>
@@ -16377,7 +16443,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="162" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B22" s="163"/>
       <c r="C22" s="163"/>
@@ -16387,10 +16453,10 @@
       <c r="G22" s="163"/>
       <c r="H22" s="164"/>
       <c r="I22" s="153" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J22" s="172" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="K22" s="172"/>
       <c r="L22" s="172"/>
@@ -16401,7 +16467,7 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="156" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B23" s="157"/>
       <c r="C23" s="157"/>
@@ -16421,7 +16487,7 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="162" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B24" s="163"/>
       <c r="C24" s="163"/>
@@ -16431,11 +16497,11 @@
       <c r="G24" s="163"/>
       <c r="H24" s="164"/>
       <c r="I24" s="153" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J24" s="170"/>
       <c r="K24" s="161" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="L24" s="161"/>
       <c r="M24" s="161"/>
@@ -16463,7 +16529,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="181" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B26" s="182"/>
       <c r="C26" s="182"/>
@@ -16473,7 +16539,7 @@
       <c r="G26" s="182"/>
       <c r="H26" s="183"/>
       <c r="I26" s="184" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="J26" s="182"/>
       <c r="K26" s="182"/>
@@ -16485,7 +16551,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="141" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B27" s="142"/>
       <c r="C27" s="142"/>
@@ -16495,7 +16561,7 @@
       <c r="G27" s="142"/>
       <c r="H27" s="143"/>
       <c r="I27" s="186" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="J27" s="187"/>
       <c r="K27" s="187"/>
@@ -16527,7 +16593,7 @@
       <c r="A29" s="149"/>
       <c r="B29" s="150"/>
       <c r="C29" s="192" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D29" s="192"/>
       <c r="E29" s="192"/>
@@ -16535,10 +16601,10 @@
       <c r="G29" s="192"/>
       <c r="H29" s="189"/>
       <c r="I29" s="153" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="J29" s="172" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K29" s="172"/>
       <c r="L29" s="172"/>
@@ -16557,10 +16623,10 @@
       <c r="G30" s="150"/>
       <c r="H30" s="189"/>
       <c r="I30" s="194" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="J30" s="195" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K30" s="195"/>
       <c r="L30" s="195"/>
@@ -16572,18 +16638,18 @@
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="149"/>
       <c r="B31" s="197" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C31" s="197"/>
       <c r="D31" s="150"/>
       <c r="E31" s="150"/>
       <c r="F31" s="150"/>
       <c r="G31" s="192" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H31" s="189"/>
       <c r="I31" s="153" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J31" s="159"/>
       <c r="K31" s="161"/>
@@ -16603,11 +16669,11 @@
       <c r="G32" s="199"/>
       <c r="H32" s="200"/>
       <c r="I32" s="153" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J32" s="159"/>
       <c r="K32" s="161" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="L32" s="161"/>
       <c r="M32" s="161"/>
@@ -16635,35 +16701,35 @@
     </row>
     <row r="34" ht="24.75" customHeight="1">
       <c r="A34" s="207" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B34" s="208" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C34" s="209"/>
       <c r="D34" s="208" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E34" s="209"/>
       <c r="F34" s="208" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="G34" s="209"/>
       <c r="H34" s="210" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="I34" s="210" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J34" s="208" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="K34" s="211"/>
       <c r="L34" s="211"/>
       <c r="M34" s="211"/>
       <c r="N34" s="209"/>
       <c r="O34" s="208" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="P34" s="212"/>
     </row>
@@ -16672,7 +16738,7 @@
       <c r="B35" s="214"/>
       <c r="C35" s="215"/>
       <c r="D35" s="214" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E35" s="215"/>
       <c r="F35" s="214"/>
@@ -16723,7 +16789,7 @@
       <c r="M36" s="223"/>
       <c r="N36" s="224"/>
       <c r="O36" s="208" t="str">
-        <f t="shared" ref="O36:O38" si="7">IF(D36="","","대한민국")</f>
+        <f t="shared" ref="O36:O38" si="6">IF(D36="","","대한민국")</f>
         <v>대한민국</v>
       </c>
       <c r="P36" s="212"/>
@@ -16731,84 +16797,84 @@
     <row r="37" ht="64.5" customHeight="1">
       <c r="A37" s="207" t="str">
         <f>IF(B37="","","2")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="B37" s="208" t="str">
         <f>IF(ISERROR(VLOOKUP('기초 자료 입력'!D27,데이터!$A$8:$E$137,4,0)),"",VLOOKUP('기초 자료 입력'!D27,데이터!$A$8:$E$137,4,0))</f>
-        <v/>
+        <v>39111611</v>
       </c>
       <c r="C37" s="209"/>
       <c r="D37" s="208" t="str">
         <f>IF(ISERROR(VLOOKUP('기초 자료 입력'!D27,데이터!$A$8:$E$137,2,0)),"",VLOOKUP('기초 자료 입력'!D27,데이터!$A$8:$E$137,2,0))</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="E37" s="209"/>
       <c r="F37" s="219" t="str">
         <f>IF('기초 자료 입력'!F27="","",'기초 자료 입력'!F27)</f>
-        <v/>
+        <v>개</v>
       </c>
       <c r="G37" s="209"/>
-      <c r="H37" s="225" t="str">
+      <c r="H37" s="225">
         <f>IF('기초 자료 입력'!G27="","",'기초 자료 입력'!G27)</f>
-        <v/>
-      </c>
-      <c r="I37" s="226" t="str">
+        <v>28</v>
+      </c>
+      <c r="I37" s="226">
         <f>IF('기초 자료 입력'!E27="","",'기초 자료 입력'!E27)</f>
-        <v/>
-      </c>
-      <c r="J37" s="222" t="str">
-        <f t="shared" ref="J37:J38" si="8">IF(B37="","",H37*I37)</f>
-        <v/>
+        <v>2950000</v>
+      </c>
+      <c r="J37" s="222">
+        <f t="shared" ref="J37:J38" si="7">IF(B37="","",H37*I37)</f>
+        <v>82600000</v>
       </c>
       <c r="K37" s="223"/>
       <c r="L37" s="223"/>
       <c r="M37" s="223"/>
       <c r="N37" s="224"/>
       <c r="O37" s="208" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f t="shared" si="6"/>
+        <v>대한민국</v>
       </c>
       <c r="P37" s="212"/>
     </row>
     <row r="38" ht="64.5" customHeight="1">
       <c r="A38" s="207" t="str">
         <f>IF(B38="","","3")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="B38" s="208" t="str">
         <f>IF(ISERROR(VLOOKUP('기초 자료 입력'!D28,데이터!$A$8:$E$137,4,0)),"",VLOOKUP('기초 자료 입력'!D28,데이터!$A$8:$E$137,4,0))</f>
-        <v/>
+        <v>39111611</v>
       </c>
       <c r="C38" s="209"/>
       <c r="D38" s="208" t="str">
         <f>IF(ISERROR(VLOOKUP('기초 자료 입력'!D28,데이터!$A$8:$E$137,2,0)),"",VLOOKUP('기초 자료 입력'!D28,데이터!$A$8:$E$137,2,0))</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="E38" s="209"/>
       <c r="F38" s="219" t="str">
         <f>IF('기초 자료 입력'!F28="","",'기초 자료 입력'!F28)</f>
-        <v/>
+        <v>개</v>
       </c>
       <c r="G38" s="227"/>
-      <c r="H38" s="225" t="str">
+      <c r="H38" s="225">
         <f>IF('기초 자료 입력'!G28="","",'기초 자료 입력'!G28)</f>
-        <v/>
-      </c>
-      <c r="I38" s="226" t="str">
+        <v>28</v>
+      </c>
+      <c r="I38" s="226">
         <f>IF('기초 자료 입력'!E28="","",'기초 자료 입력'!E28)</f>
-        <v/>
-      </c>
-      <c r="J38" s="222" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <v>2950000</v>
+      </c>
+      <c r="J38" s="222">
+        <f t="shared" si="7"/>
+        <v>82600000</v>
       </c>
       <c r="K38" s="223"/>
       <c r="L38" s="223"/>
       <c r="M38" s="223"/>
       <c r="N38" s="224"/>
       <c r="O38" s="208" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f t="shared" si="6"/>
+        <v>대한민국</v>
       </c>
       <c r="P38" s="212"/>
     </row>
@@ -16822,11 +16888,11 @@
       <c r="G39" s="230"/>
       <c r="H39" s="231"/>
       <c r="I39" s="232" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J39" s="233">
         <f>SUM(J36:N38)/1.1</f>
-        <v>75090909.090909079</v>
+        <v>225272727.27272725</v>
       </c>
       <c r="K39" s="234"/>
       <c r="L39" s="234"/>
@@ -16845,11 +16911,11 @@
       <c r="G40" s="238"/>
       <c r="H40" s="239"/>
       <c r="I40" s="232" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="J40" s="233">
         <f>J39*0.1</f>
-        <v>7509090.9090909082</v>
+        <v>22527272.727272727</v>
       </c>
       <c r="K40" s="234"/>
       <c r="L40" s="234"/>
@@ -16868,11 +16934,11 @@
       <c r="G41" s="242"/>
       <c r="H41" s="243"/>
       <c r="I41" s="232" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J41" s="244">
         <f>J39+J40</f>
-        <v>82599999.999999985</v>
+        <v>247799999.99999997</v>
       </c>
       <c r="K41" s="245"/>
       <c r="L41" s="245"/>
@@ -16883,23 +16949,23 @@
     </row>
     <row r="42" ht="18">
       <c r="A42" s="247" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B42" s="248"/>
       <c r="C42" s="249"/>
       <c r="D42" s="250" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E42" s="251"/>
       <c r="F42" s="251"/>
       <c r="G42" s="251"/>
       <c r="H42" s="252"/>
       <c r="I42" s="253" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J42" s="249"/>
       <c r="K42" s="251" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="L42" s="251"/>
       <c r="M42" s="251"/>
@@ -17456,7 +17522,7 @@
     <row r="1" ht="33" customHeight="1"/>
     <row r="2" ht="69.75" customHeight="1">
       <c r="A2" s="257" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B2" s="258"/>
       <c r="C2" s="258"/>
@@ -17484,7 +17550,7 @@
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="263" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B4" s="264"/>
       <c r="C4" s="265" t="str">
@@ -17499,34 +17565,34 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="268" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B5" s="264" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C5" s="264" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D5" s="269" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E5" s="269" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F5" s="269" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G5" s="269" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="H5" s="270" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="263"/>
       <c r="B6" s="264" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C6" s="264"/>
       <c r="D6" s="264"/>
@@ -17556,7 +17622,7 @@
         <v>28</v>
       </c>
       <c r="F7" s="276" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G7" s="277">
         <f>E7</f>
@@ -17578,33 +17644,33 @@
       <c r="H8" s="278"/>
     </row>
     <row r="9" ht="38.100000000000001" customHeight="1">
-      <c r="A9" s="271" t="str">
+      <c r="A9" s="271">
         <f>IF(B9="","",A7+1)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="B9" s="272" t="str">
         <f>IF('기초 자료 입력'!$L$27="","",'기초 자료 입력'!$L$27)</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="C9" s="273" t="str">
         <f>IF('기초 자료 입력'!F27="","",'기초 자료 입력'!F27)</f>
-        <v/>
-      </c>
-      <c r="D9" s="274" t="str">
+        <v>개</v>
+      </c>
+      <c r="D9" s="274">
         <f>IF('기초 자료 입력'!$E$27="","",'기초 자료 입력'!$E$27)</f>
-        <v/>
-      </c>
-      <c r="E9" s="275" t="str">
+        <v>2950000</v>
+      </c>
+      <c r="E9" s="275">
         <f>IF('기초 자료 입력'!$G$27="","",'기초 자료 입력'!$G$27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="F9" s="276" t="str">
         <f>IF(B9="","","-")</f>
-        <v/>
-      </c>
-      <c r="G9" s="277" t="str">
+        <v>-</v>
+      </c>
+      <c r="G9" s="277">
         <f>E9</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="H9" s="278"/>
     </row>
@@ -17612,7 +17678,7 @@
       <c r="A10" s="271"/>
       <c r="B10" s="272" t="str">
         <f>IF('기초 자료 입력'!$K$27="","",'기초 자료 입력'!$K$27)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="C10" s="279"/>
       <c r="D10" s="280"/>
@@ -17622,33 +17688,33 @@
       <c r="H10" s="278"/>
     </row>
     <row r="11" ht="38.100000000000001" customHeight="1">
-      <c r="A11" s="282" t="str">
+      <c r="A11" s="282">
         <f>IF(B11="","",A9+1)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="B11" s="272" t="str">
         <f>IF('기초 자료 입력'!$L$27="","",'기초 자료 입력'!$L$27)</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="C11" s="273" t="str">
         <f>IF('기초 자료 입력'!F29="","",'기초 자료 입력'!F29)</f>
-        <v/>
-      </c>
-      <c r="D11" s="274" t="str">
+        <v>개</v>
+      </c>
+      <c r="D11" s="274">
         <f>IF('기초 자료 입력'!$E$27="","",'기초 자료 입력'!$E$27)</f>
-        <v/>
-      </c>
-      <c r="E11" s="277" t="str">
+        <v>2950000</v>
+      </c>
+      <c r="E11" s="277">
         <f>IF('기초 자료 입력'!$G$27="","",'기초 자료 입력'!$G$27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="F11" s="283" t="str">
         <f>IF(B11="","","-")</f>
-        <v/>
-      </c>
-      <c r="G11" s="277" t="str">
+        <v>-</v>
+      </c>
+      <c r="G11" s="277">
         <f>E11</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="H11" s="284"/>
     </row>
@@ -17656,7 +17722,7 @@
       <c r="A12" s="271"/>
       <c r="B12" s="272" t="str">
         <f>IF('기초 자료 입력'!$K$27="","",'기초 자료 입력'!$K$27)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="C12" s="279"/>
       <c r="D12" s="280"/>
@@ -17666,33 +17732,33 @@
       <c r="H12" s="278"/>
     </row>
     <row r="13" ht="38.100000000000001" customHeight="1">
-      <c r="A13" s="282" t="str">
+      <c r="A13" s="282">
         <f>IF(B13="","",A11+1)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="B13" s="272" t="str">
         <f>IF('기초 자료 입력'!$L$27="","",'기초 자료 입력'!$L$27)</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="C13" s="273" t="str">
         <f>IF('기초 자료 입력'!F31="","",'기초 자료 입력'!F31)</f>
         <v/>
       </c>
-      <c r="D13" s="274" t="str">
+      <c r="D13" s="274">
         <f>IF('기초 자료 입력'!$E$27="","",'기초 자료 입력'!$E$27)</f>
-        <v/>
-      </c>
-      <c r="E13" s="277" t="str">
+        <v>2950000</v>
+      </c>
+      <c r="E13" s="277">
         <f>IF('기초 자료 입력'!$G$27="","",'기초 자료 입력'!$G$27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="F13" s="283" t="str">
         <f>IF(B13="","","-")</f>
-        <v/>
-      </c>
-      <c r="G13" s="277" t="str">
+        <v>-</v>
+      </c>
+      <c r="G13" s="277">
         <f>E13</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="H13" s="284"/>
       <c r="I13" s="285"/>
@@ -17703,7 +17769,7 @@
       <c r="A14" s="271"/>
       <c r="B14" s="272" t="str">
         <f>IF('기초 자료 입력'!$K$27="","",'기초 자료 입력'!$K$27)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="C14" s="279"/>
       <c r="D14" s="280"/>
@@ -17715,33 +17781,33 @@
       <c r="J14" s="285"/>
     </row>
     <row r="15" ht="38.100000000000001" customHeight="1">
-      <c r="A15" s="282" t="str">
+      <c r="A15" s="282">
         <f>IF(B15="","",A13+1)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="B15" s="272" t="str">
         <f>IF('기초 자료 입력'!$L$27="","",'기초 자료 입력'!$L$27)</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="C15" s="273" t="str">
         <f>IF('기초 자료 입력'!F33="","",'기초 자료 입력'!F33)</f>
         <v/>
       </c>
-      <c r="D15" s="274" t="str">
+      <c r="D15" s="274">
         <f>IF('기초 자료 입력'!$E$27="","",'기초 자료 입력'!$E$27)</f>
-        <v/>
-      </c>
-      <c r="E15" s="277" t="str">
+        <v>2950000</v>
+      </c>
+      <c r="E15" s="277">
         <f>IF('기초 자료 입력'!$G$27="","",'기초 자료 입력'!$G$27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="F15" s="283" t="str">
         <f>IF(B15="","","-")</f>
-        <v/>
-      </c>
-      <c r="G15" s="277" t="str">
+        <v>-</v>
+      </c>
+      <c r="G15" s="277">
         <f>E15</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="H15" s="284"/>
     </row>
@@ -17749,7 +17815,7 @@
       <c r="A16" s="271"/>
       <c r="B16" s="272" t="str">
         <f>IF('기초 자료 입력'!$K$27="","",'기초 자료 입력'!$K$27)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="C16" s="279"/>
       <c r="D16" s="280"/>
@@ -17759,33 +17825,33 @@
       <c r="H16" s="278"/>
     </row>
     <row r="17" ht="38.100000000000001" customHeight="1">
-      <c r="A17" s="282" t="str">
+      <c r="A17" s="282">
         <f>IF(B17="","",A15+1)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="B17" s="272" t="str">
         <f>IF('기초 자료 입력'!$L$27="","",'기초 자료 입력'!$L$27)</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="C17" s="273" t="str">
         <f>IF('기초 자료 입력'!F35="","",'기초 자료 입력'!F35)</f>
         <v/>
       </c>
-      <c r="D17" s="274" t="str">
+      <c r="D17" s="274">
         <f>IF('기초 자료 입력'!$E$27="","",'기초 자료 입력'!$E$27)</f>
-        <v/>
-      </c>
-      <c r="E17" s="277" t="str">
+        <v>2950000</v>
+      </c>
+      <c r="E17" s="277">
         <f>IF('기초 자료 입력'!$G$27="","",'기초 자료 입력'!$G$27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="F17" s="283" t="str">
         <f>IF(B17="","","-")</f>
-        <v/>
-      </c>
-      <c r="G17" s="277" t="str">
+        <v>-</v>
+      </c>
+      <c r="G17" s="277">
         <f>E17</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="H17" s="284"/>
     </row>
@@ -17793,7 +17859,7 @@
       <c r="A18" s="271"/>
       <c r="B18" s="272" t="str">
         <f>IF('기초 자료 입력'!$K$27="","",'기초 자료 입력'!$K$27)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="C18" s="279"/>
       <c r="D18" s="280"/>
@@ -17803,33 +17869,33 @@
       <c r="H18" s="278"/>
     </row>
     <row r="19" ht="38.100000000000001" customHeight="1">
-      <c r="A19" s="282" t="str">
+      <c r="A19" s="282">
         <f>IF(B19="","",A17+1)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="B19" s="272" t="str">
         <f>IF('기초 자료 입력'!$L$27="","",'기초 자료 입력'!$L$27)</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="C19" s="273" t="str">
         <f>IF('기초 자료 입력'!F37="","",'기초 자료 입력'!F37)</f>
         <v/>
       </c>
-      <c r="D19" s="274" t="str">
+      <c r="D19" s="274">
         <f>IF('기초 자료 입력'!$E$27="","",'기초 자료 입력'!$E$27)</f>
-        <v/>
-      </c>
-      <c r="E19" s="277" t="str">
+        <v>2950000</v>
+      </c>
+      <c r="E19" s="277">
         <f>IF('기초 자료 입력'!$G$27="","",'기초 자료 입력'!$G$27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="F19" s="283" t="str">
         <f>IF(B19="","","-")</f>
-        <v/>
-      </c>
-      <c r="G19" s="277" t="str">
+        <v>-</v>
+      </c>
+      <c r="G19" s="277">
         <f>E19</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="H19" s="284"/>
     </row>
@@ -17837,7 +17903,7 @@
       <c r="A20" s="271"/>
       <c r="B20" s="272" t="str">
         <f>IF('기초 자료 입력'!$K$27="","",'기초 자료 입력'!$K$27)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="C20" s="279"/>
       <c r="D20" s="280"/>
@@ -17847,33 +17913,33 @@
       <c r="H20" s="278"/>
     </row>
     <row r="21" ht="38.100000000000001" customHeight="1">
-      <c r="A21" s="282" t="str">
+      <c r="A21" s="282">
         <f>IF(B21="","",A19+1)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="B21" s="272" t="str">
         <f>IF('기초 자료 입력'!$L$27="","",'기초 자료 입력'!$L$27)</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="C21" s="273" t="str">
         <f>IF('기초 자료 입력'!F39="","",'기초 자료 입력'!F39)</f>
         <v/>
       </c>
-      <c r="D21" s="274" t="str">
+      <c r="D21" s="274">
         <f>IF('기초 자료 입력'!$E$27="","",'기초 자료 입력'!$E$27)</f>
-        <v/>
-      </c>
-      <c r="E21" s="277" t="str">
+        <v>2950000</v>
+      </c>
+      <c r="E21" s="277">
         <f>IF('기초 자료 입력'!$G$27="","",'기초 자료 입력'!$G$27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="F21" s="283" t="str">
         <f>IF(B21="","","-")</f>
-        <v/>
-      </c>
-      <c r="G21" s="277" t="str">
+        <v>-</v>
+      </c>
+      <c r="G21" s="277">
         <f>E21</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="H21" s="284"/>
     </row>
@@ -17881,7 +17947,7 @@
       <c r="A22" s="271"/>
       <c r="B22" s="272" t="str">
         <f>IF('기초 자료 입력'!$K$27="","",'기초 자료 입력'!$K$27)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="C22" s="279"/>
       <c r="D22" s="280"/>
@@ -17891,33 +17957,33 @@
       <c r="H22" s="278"/>
     </row>
     <row r="23" ht="38.100000000000001" customHeight="1">
-      <c r="A23" s="282" t="str">
+      <c r="A23" s="282">
         <f>IF(B23="","",A21+1)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="B23" s="272" t="str">
         <f>IF('기초 자료 입력'!$L$27="","",'기초 자료 입력'!$L$27)</f>
-        <v/>
+        <v>투광조명</v>
       </c>
       <c r="C23" s="273" t="str">
         <f>IF('기초 자료 입력'!F41="","",'기초 자료 입력'!F41)</f>
         <v/>
       </c>
-      <c r="D23" s="274" t="str">
+      <c r="D23" s="274">
         <f>IF('기초 자료 입력'!$E$27="","",'기초 자료 입력'!$E$27)</f>
-        <v/>
-      </c>
-      <c r="E23" s="277" t="str">
+        <v>2950000</v>
+      </c>
+      <c r="E23" s="277">
         <f>IF('기초 자료 입력'!$G$27="","",'기초 자료 입력'!$G$27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="F23" s="283" t="str">
         <f>IF(B23="","","-")</f>
-        <v/>
-      </c>
-      <c r="G23" s="277" t="str">
+        <v>-</v>
+      </c>
+      <c r="G23" s="277">
         <f>E23</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="H23" s="284"/>
     </row>
@@ -17925,7 +17991,7 @@
       <c r="A24" s="271"/>
       <c r="B24" s="272" t="str">
         <f>IF('기초 자료 입력'!$K$27="","",'기초 자료 입력'!$K$27)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="C24" s="279"/>
       <c r="D24" s="280"/>
@@ -18854,7 +18920,7 @@
   <sheetData>
     <row r="1" ht="98.25" customHeight="1">
       <c r="B1" s="287" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C1" s="287"/>
       <c r="D1" s="287"/>
@@ -18886,7 +18952,7 @@
     </row>
     <row r="3" ht="20.100000000000001" customHeight="1">
       <c r="B3" s="289" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C3" s="291" t="str">
         <f>'기초 자료 입력'!$D$7</f>
@@ -18903,7 +18969,7 @@
     </row>
     <row r="4" ht="20.100000000000001" customHeight="1">
       <c r="B4" s="289" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C4" s="293">
         <f>'기초 자료 입력'!$D$9</f>
@@ -18920,7 +18986,7 @@
     </row>
     <row r="5" ht="20.100000000000001" customHeight="1">
       <c r="B5" s="289" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C5" s="293">
         <f>'기초 자료 입력'!$D$12</f>
@@ -18950,7 +19016,7 @@
     </row>
     <row r="7" ht="20.100000000000001" customHeight="1">
       <c r="B7" s="295" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C7" s="289"/>
       <c r="D7" s="289"/>
@@ -18964,7 +19030,7 @@
     </row>
     <row r="8" ht="34.5" customHeight="1">
       <c r="B8" s="297" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C8" s="298"/>
       <c r="D8" s="298" t="s">
@@ -18973,13 +19039,13 @@
       <c r="E8" s="298"/>
       <c r="F8" s="298"/>
       <c r="G8" s="298" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H8" s="298" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="I8" s="299" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J8" s="289"/>
       <c r="K8" s="289"/>
@@ -19016,27 +19082,28 @@
     <row r="10" ht="49.5" customHeight="1">
       <c r="B10" s="304" t="str">
         <f>IF('기초 자료 입력'!D27="","",'기초 자료 입력'!D27)</f>
-        <v/>
+        <v>ARENA-600(3000K)</v>
       </c>
       <c r="C10" s="305"/>
       <c r="D10" s="306" t="str">
         <f>IF('기초 자료 입력'!K27="","",'기초 자료 입력'!K27)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="E10" s="307"/>
       <c r="F10" s="308"/>
       <c r="G10" s="309" t="str">
         <f>IF('기초 자료 입력'!F27="","",'기초 자료 입력'!F27)</f>
-        <v/>
-      </c>
-      <c r="H10" s="309" t="str">
+        <v>개</v>
+      </c>
+      <c r="H10" s="309">
         <f>IF('기초 자료 입력'!G27="","",'기초 자료 입력'!G27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="I10" s="310" t="str">
-        <f t="shared" ref="I10:I14" si="9">IF(B10="","","납품장소
+        <f t="shared" ref="I10:I14" si="8">IF(B10="","","납품장소
 하차도")</f>
-        <v/>
+        <v xml:space="preserve">납품장소
+하차도</v>
       </c>
       <c r="J10" s="289"/>
       <c r="K10" s="289"/>
@@ -19044,26 +19111,27 @@
     <row r="11" ht="49.5" customHeight="1">
       <c r="B11" s="311" t="str">
         <f>IF('기초 자료 입력'!D28="","",'기초 자료 입력'!D28)</f>
-        <v/>
+        <v>ARENA-600(3000K)</v>
       </c>
       <c r="C11" s="308"/>
       <c r="D11" s="306" t="str">
         <f>IF('기초 자료 입력'!K28="","",'기초 자료 입력'!K28)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="E11" s="307"/>
       <c r="F11" s="308"/>
       <c r="G11" s="309" t="str">
         <f>IF('기초 자료 입력'!F28="","",'기초 자료 입력'!F28)</f>
-        <v/>
-      </c>
-      <c r="H11" s="309" t="str">
+        <v>개</v>
+      </c>
+      <c r="H11" s="309">
         <f>IF('기초 자료 입력'!G28="","",'기초 자료 입력'!G28)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="I11" s="310" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">납품장소
+하차도</v>
       </c>
       <c r="J11" s="289"/>
       <c r="K11" s="289"/>
@@ -19071,26 +19139,27 @@
     <row r="12" ht="49.5" customHeight="1">
       <c r="B12" s="311" t="str">
         <f>IF('기초 자료 입력'!D29="","",'기초 자료 입력'!D29)</f>
-        <v/>
+        <v>ARENA-600(3000K)</v>
       </c>
       <c r="C12" s="308"/>
       <c r="D12" s="306" t="str">
         <f>IF('기초 자료 입력'!K29="","",'기초 자료 입력'!K29)</f>
-        <v/>
+        <v xml:space="preserve"> LED투광등기구 ARENA-600(3000K) 600W  </v>
       </c>
       <c r="E12" s="307"/>
       <c r="F12" s="308"/>
       <c r="G12" s="309" t="str">
         <f>IF('기초 자료 입력'!F29="","",'기초 자료 입력'!F29)</f>
-        <v/>
-      </c>
-      <c r="H12" s="309" t="str">
+        <v>개</v>
+      </c>
+      <c r="H12" s="309">
         <f>IF('기초 자료 입력'!G29="","",'기초 자료 입력'!G29)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="I12" s="310" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">납품장소
+하차도</v>
       </c>
       <c r="J12" s="289"/>
       <c r="K12" s="289"/>
@@ -19116,7 +19185,7 @@
         <v/>
       </c>
       <c r="I13" s="310" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J13" s="289"/>
@@ -19143,7 +19212,7 @@
         <v/>
       </c>
       <c r="I14" s="310" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J14" s="289"/>
@@ -19218,7 +19287,7 @@
       <c r="D20" s="289"/>
       <c r="E20" s="289"/>
       <c r="F20" s="289" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G20" s="289"/>
       <c r="H20" s="289"/>
@@ -19232,10 +19301,10 @@
       <c r="D21" s="289"/>
       <c r="E21" s="289"/>
       <c r="F21" s="317" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G21" s="290" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="H21" s="290"/>
       <c r="I21" s="290"/>
@@ -19248,10 +19317,10 @@
       <c r="D22" s="289"/>
       <c r="E22" s="289"/>
       <c r="F22" s="317" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="G22" s="290" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="H22" s="290"/>
       <c r="I22" s="290"/>
@@ -19264,14 +19333,14 @@
       <c r="D23" s="289"/>
       <c r="E23" s="289"/>
       <c r="F23" s="317" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G23" s="290" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="H23" s="290"/>
       <c r="I23" s="290" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="J23" s="289"/>
       <c r="K23" s="289"/>
@@ -19318,7 +19387,7 @@
       <c r="D27" s="316"/>
       <c r="E27" s="316"/>
       <c r="F27" s="318" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="G27" s="318"/>
       <c r="H27" s="318"/>
@@ -19332,7 +19401,7 @@
       <c r="D28" s="289"/>
       <c r="E28" s="289"/>
       <c r="F28" s="317" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G28" s="290"/>
       <c r="H28" s="290"/>
@@ -19346,7 +19415,7 @@
       <c r="D29" s="289"/>
       <c r="E29" s="289"/>
       <c r="F29" s="317" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="G29" s="290"/>
       <c r="H29" s="290"/>
@@ -19360,12 +19429,12 @@
       <c r="D30" s="289"/>
       <c r="E30" s="289"/>
       <c r="F30" s="317" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G30" s="290"/>
       <c r="H30" s="290"/>
       <c r="I30" s="290" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="J30" s="289"/>
       <c r="K30" s="289"/>
@@ -19920,7 +19989,7 @@
   <sheetData>
     <row r="1" s="321" customFormat="1" ht="47.25" customHeight="1">
       <c r="A1" s="322" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B1" s="322"/>
       <c r="C1" s="322"/>
@@ -19930,7 +19999,7 @@
       <c r="G1" s="322"/>
       <c r="H1" s="323"/>
       <c r="I1" s="323" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J1" s="323"/>
       <c r="K1" s="323"/>
@@ -20074,7 +20143,7 @@
     </row>
     <row r="8" s="321" customFormat="1" ht="293.25" customHeight="1">
       <c r="B8" s="332" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C8" s="332"/>
       <c r="D8" s="333"/>
@@ -20094,7 +20163,7 @@
     </row>
     <row r="9" s="321" customFormat="1" ht="30.75" customHeight="1">
       <c r="A9" s="334" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B9" s="334"/>
       <c r="C9" s="334"/>
@@ -20118,7 +20187,7 @@
     <row r="10" s="324" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="A10" s="326"/>
       <c r="B10" s="335" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C10" s="336"/>
       <c r="D10" s="337" t="str">
@@ -20144,7 +20213,7 @@
     <row r="11" s="324" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="A11" s="326"/>
       <c r="B11" s="340" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C11" s="341"/>
       <c r="D11" s="342">
@@ -20170,11 +20239,11 @@
     <row r="12" s="324" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="A12" s="326"/>
       <c r="B12" s="345" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C12" s="346"/>
       <c r="D12" s="347" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E12" s="348"/>
       <c r="F12" s="349"/>
@@ -20272,7 +20341,7 @@
     </row>
     <row r="17" s="321" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="B17" s="362" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C17" s="363"/>
       <c r="D17" s="363"/>
@@ -20372,7 +20441,7 @@
     </row>
     <row r="22" s="321" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="B22" s="367" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C22" s="368"/>
       <c r="D22" s="368"/>
@@ -20470,7 +20539,7 @@
     </row>
     <row r="27" s="321" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="B27" s="362" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C27" s="363"/>
       <c r="D27" s="363"/>
@@ -20570,7 +20639,7 @@
     </row>
     <row r="32" s="321" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="B32" s="367" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C32" s="368"/>
       <c r="D32" s="368"/>
@@ -20669,7 +20738,7 @@
     </row>
     <row r="37" s="321" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="B37" s="362" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C37" s="363"/>
       <c r="D37" s="363"/>
@@ -20769,7 +20838,7 @@
     </row>
     <row r="42" s="321" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="B42" s="367" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C42" s="368"/>
       <c r="D42" s="368"/>
@@ -20868,7 +20937,7 @@
     </row>
     <row r="47" s="321" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="B47" s="362" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C47" s="363"/>
       <c r="D47" s="363"/>
@@ -20968,7 +21037,7 @@
     </row>
     <row r="52" s="321" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="B52" s="367" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C52" s="368"/>
       <c r="D52" s="368"/>
@@ -21067,7 +21136,7 @@
     </row>
     <row r="57" s="321" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="B57" s="367" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C57" s="368"/>
       <c r="D57" s="368"/>

--- a/static/templates/delivery_template.xlsx
+++ b/static/templates/delivery_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="데이터" sheetId="1" state="visible" r:id="rId6"/>
@@ -13944,19 +13944,19 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00DC0033-0077-4844-A8B3-002200230062}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{008E0033-001F-4B8A-9AB6-0047009C00D0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"유, 무"</xm:f>
           </x14:formula1>
           <xm:sqref>D21</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{000A009C-00C0-40E1-A400-006400BF00C3}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00FE0075-0064-4E1F-9AFC-00F7000D00D1}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"청, 기관, 교,  사업소"</xm:f>
           </x14:formula1>
           <xm:sqref>D20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{001E00D4-00C2-4E56-BF66-00EE00570091}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00B900DC-00B1-4862-A1E3-001B00F70096}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1,2,3"</xm:f>
           </x14:formula1>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="C13" s="270" t="str">
         <f>IF('기초 자료 입력'!F29="","",'기초 자료 입력'!F29)</f>
-        <v/>
+        <v>개</v>
       </c>
       <c r="D13" s="271">
         <f>IF('기초 자료 입력'!$E$29="","",'기초 자료 입력'!$E$29)</f>
